--- a/dat/xls/SpeciesList.xlsx
+++ b/dat/xls/SpeciesList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Studium_KIT\Master_GOEK\Masterarbeit\dat\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9A2BCB-3D5E-4AB5-B523-F89646B86300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA1888C-866B-4D62-BFCB-9835B09780F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="SpeciesID" sheetId="1" r:id="rId1"/>
     <sheet name="GenusID" sheetId="2" r:id="rId2"/>
     <sheet name="Dictionary" sheetId="3" r:id="rId3"/>
+    <sheet name="Options" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="188">
   <si>
     <t>SpeciesID</t>
   </si>
@@ -469,13 +470,163 @@
   </si>
   <si>
     <t>triflora</t>
+  </si>
+  <si>
+    <t>Searsia</t>
+  </si>
+  <si>
+    <t>dentata</t>
+  </si>
+  <si>
+    <t>Ehretia rigida</t>
+  </si>
+  <si>
+    <t>Ehretia</t>
+  </si>
+  <si>
+    <t>rigida</t>
+  </si>
+  <si>
+    <t>Berchemia zeyheri</t>
+  </si>
+  <si>
+    <t>Afrocanthium mundianum</t>
+  </si>
+  <si>
+    <t>Strychnos pungens</t>
+  </si>
+  <si>
+    <t>Strychnos cocculoides</t>
+  </si>
+  <si>
+    <t>Strychnos spinosa</t>
+  </si>
+  <si>
+    <t>Mimusops zeyheri</t>
+  </si>
+  <si>
+    <t>Psiadia punctulata</t>
+  </si>
+  <si>
+    <t>Vachellia tortilis</t>
+  </si>
+  <si>
+    <t>Vangueria madagascariensis</t>
+  </si>
+  <si>
+    <t>Ptaeroxylon obliquum</t>
+  </si>
+  <si>
+    <t>Schotia brachypetala</t>
+  </si>
+  <si>
+    <t>Brachylaena rotundata</t>
+  </si>
+  <si>
+    <t>Afrocanthium</t>
+  </si>
+  <si>
+    <t>mundianum</t>
+  </si>
+  <si>
+    <t>Berchemia</t>
+  </si>
+  <si>
+    <t>Brachylaena</t>
+  </si>
+  <si>
+    <t>rotundata</t>
+  </si>
+  <si>
+    <t>Mimusops</t>
+  </si>
+  <si>
+    <t>Psiadia</t>
+  </si>
+  <si>
+    <t>punctulata</t>
+  </si>
+  <si>
+    <t>Ptaeroxylon</t>
+  </si>
+  <si>
+    <t>obliquum</t>
+  </si>
+  <si>
+    <t>Schotia</t>
+  </si>
+  <si>
+    <t>brachypetala</t>
+  </si>
+  <si>
+    <t>cocculoides</t>
+  </si>
+  <si>
+    <t>pungens</t>
+  </si>
+  <si>
+    <t>spinosa</t>
+  </si>
+  <si>
+    <t>Vachellia</t>
+  </si>
+  <si>
+    <t>tortilis</t>
+  </si>
+  <si>
+    <t>Ancylobothrys capensis</t>
+  </si>
+  <si>
+    <t>Ancylobothrys</t>
+  </si>
+  <si>
+    <t>Searsia leptodictya</t>
+  </si>
+  <si>
+    <t>leptodictya</t>
+  </si>
+  <si>
+    <t>americana</t>
+  </si>
+  <si>
+    <t>Ximenia americana</t>
+  </si>
+  <si>
+    <t>Senegalif cf burkei</t>
+  </si>
+  <si>
+    <t>Block_1</t>
+  </si>
+  <si>
+    <t>Block_2</t>
+  </si>
+  <si>
+    <t>Block_3</t>
+  </si>
+  <si>
+    <t>Block_4</t>
+  </si>
+  <si>
+    <t>Block_5</t>
+  </si>
+  <si>
+    <t>Block_6</t>
+  </si>
+  <si>
+    <t>Block_7</t>
+  </si>
+  <si>
+    <t>Block_8</t>
+  </si>
+  <si>
+    <t>Presence</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,6 +757,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -963,10 +1120,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1012,7 +1170,28 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1322,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -2177,6 +2356,366 @@
         <v>125</v>
       </c>
     </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <f>_xlfn.XLOOKUP(D48,GenusID!B:B,GenusID!A:A)</f>
+        <v>37</v>
+      </c>
+      <c r="C48" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <f>_xlfn.XLOOKUP(D49,GenusID!B:B,GenusID!A:A)</f>
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <f>_xlfn.XLOOKUP(D50,GenusID!B:B,GenusID!A:A)</f>
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <f>_xlfn.XLOOKUP(D51,GenusID!B:B,GenusID!A:A)</f>
+        <v>40</v>
+      </c>
+      <c r="C51" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <f>_xlfn.XLOOKUP(D52,GenusID!B:B,GenusID!A:A)</f>
+        <v>41</v>
+      </c>
+      <c r="C52" t="s">
+        <v>144</v>
+      </c>
+      <c r="D52" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <f>_xlfn.XLOOKUP(D53,GenusID!B:B,GenusID!A:A)</f>
+        <v>42</v>
+      </c>
+      <c r="C53" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53" t="s">
+        <v>157</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <f>_xlfn.XLOOKUP(D54,GenusID!B:B,GenusID!A:A)</f>
+        <v>43</v>
+      </c>
+      <c r="C54" t="s">
+        <v>154</v>
+      </c>
+      <c r="D54" t="s">
+        <v>158</v>
+      </c>
+      <c r="E54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <f>_xlfn.XLOOKUP(D55,GenusID!B:B,GenusID!A:A)</f>
+        <v>44</v>
+      </c>
+      <c r="C55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <f>_xlfn.XLOOKUP(D56,GenusID!B:B,GenusID!A:A)</f>
+        <v>45</v>
+      </c>
+      <c r="C56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <f>_xlfn.XLOOKUP(D57,GenusID!B:B,GenusID!A:A)</f>
+        <v>46</v>
+      </c>
+      <c r="C57" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" t="s">
+        <v>163</v>
+      </c>
+      <c r="E57" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <f>_xlfn.XLOOKUP(D58,GenusID!B:B,GenusID!A:A)</f>
+        <v>47</v>
+      </c>
+      <c r="C58" t="s">
+        <v>153</v>
+      </c>
+      <c r="D58" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <f>_xlfn.XLOOKUP(D59,GenusID!B:B,GenusID!A:A)</f>
+        <v>31</v>
+      </c>
+      <c r="C59" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" t="s">
+        <v>108</v>
+      </c>
+      <c r="E59" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <f>_xlfn.XLOOKUP(D60,GenusID!B:B,GenusID!A:A)</f>
+        <v>31</v>
+      </c>
+      <c r="C60" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <f>_xlfn.XLOOKUP(D61,GenusID!B:B,GenusID!A:A)</f>
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>147</v>
+      </c>
+      <c r="D61" t="s">
+        <v>108</v>
+      </c>
+      <c r="E61" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <f>_xlfn.XLOOKUP(D62,GenusID!B:B,GenusID!A:A)</f>
+        <v>48</v>
+      </c>
+      <c r="C62" t="s">
+        <v>150</v>
+      </c>
+      <c r="D62" t="s">
+        <v>170</v>
+      </c>
+      <c r="E62" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <f>_xlfn.XLOOKUP(D63,GenusID!B:B,GenusID!A:A)</f>
+        <v>33</v>
+      </c>
+      <c r="C63" t="s">
+        <v>151</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <f>_xlfn.XLOOKUP(D64,GenusID!B:B,GenusID!A:A)</f>
+        <v>49</v>
+      </c>
+      <c r="C64" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <f>_xlfn.XLOOKUP(D65,GenusID!B:B,GenusID!A:A)</f>
+        <v>39</v>
+      </c>
+      <c r="C65" t="s">
+        <v>174</v>
+      </c>
+      <c r="D65" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <f>_xlfn.XLOOKUP(D66,GenusID!B:B,GenusID!A:A)</f>
+        <v>35</v>
+      </c>
+      <c r="C66" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <f>_xlfn.XLOOKUP(D67,GenusID!B:B,GenusID!A:A)</f>
+        <v>30</v>
+      </c>
+      <c r="C67" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" t="s">
+        <v>105</v>
+      </c>
+      <c r="E67" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2184,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -2488,6 +3027,110 @@
         <v>Ziziphus</v>
       </c>
     </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2495,7 +3138,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E23134-F139-46B0-B913-F428D0448CB8}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -2505,7 +3148,7 @@
     <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2521,8 +3164,32 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -2534,8 +3201,32 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2551,8 +3242,32 @@
       <c r="E3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2568,8 +3283,32 @@
       <c r="E4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2585,13 +3324,37 @@
       <c r="E5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2602,13 +3365,37 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -2619,13 +3406,37 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2636,13 +3447,37 @@
       <c r="E8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -2653,8 +3488,32 @@
       <c r="E9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2670,13 +3529,37 @@
       <c r="E10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
@@ -2687,13 +3570,37 @@
       <c r="E11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
@@ -2704,8 +3611,32 @@
       <c r="E12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2721,13 +3652,37 @@
       <c r="E13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
@@ -2738,8 +3693,32 @@
       <c r="E14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2755,8 +3734,32 @@
       <c r="E15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2772,8 +3775,32 @@
       <c r="E16" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2789,8 +3816,32 @@
       <c r="E17" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2806,13 +3857,37 @@
       <c r="E18" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
         <v>48</v>
@@ -2823,13 +3898,37 @@
       <c r="E19" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
         <v>51</v>
@@ -2840,13 +3939,37 @@
       <c r="E20" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
         <v>53</v>
@@ -2857,13 +3980,37 @@
       <c r="E21" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
         <v>55</v>
@@ -2874,13 +4021,37 @@
       <c r="E22" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
         <v>57</v>
@@ -2891,8 +4062,32 @@
       <c r="E23" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2908,8 +4103,32 @@
       <c r="E24" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2925,8 +4144,32 @@
       <c r="E25" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2942,8 +4185,32 @@
       <c r="E26" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2959,13 +4226,37 @@
       <c r="E27" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
         <v>70</v>
@@ -2976,13 +4267,37 @@
       <c r="E28" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
@@ -2993,8 +4308,32 @@
       <c r="E29" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3010,8 +4349,32 @@
       <c r="E30" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3027,8 +4390,32 @@
       <c r="E31" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3044,13 +4431,37 @@
       <c r="E32" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
         <v>84</v>
@@ -3061,8 +4472,32 @@
       <c r="E33" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3078,8 +4513,32 @@
       <c r="E34" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3095,13 +4554,37 @@
       <c r="E35" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
         <v>92</v>
@@ -3112,13 +4595,37 @@
       <c r="E36" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
         <v>95</v>
@@ -3129,8 +4636,32 @@
       <c r="E37" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3146,8 +4677,32 @@
       <c r="E38" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3163,8 +4718,32 @@
       <c r="E39" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3180,8 +4759,32 @@
       <c r="E40" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3197,13 +4800,37 @@
       <c r="E41" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
         <v>110</v>
@@ -3214,8 +4841,32 @@
       <c r="E42" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3231,8 +4882,32 @@
       <c r="E43" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3248,8 +4923,32 @@
       <c r="E44" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3265,8 +4964,32 @@
       <c r="E45" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3282,8 +5005,32 @@
       <c r="E46" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3299,8 +5046,32 @@
       <c r="E47" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3316,8 +5087,32 @@
       <c r="E48" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3333,8 +5128,32 @@
       <c r="E49" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3350,8 +5169,32 @@
       <c r="E50" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3361,10 +5204,738 @@
       <c r="C51" t="s">
         <v>135</v>
       </c>
+      <c r="D51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" t="s">
+        <v>139</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" t="s">
+        <v>142</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53" t="s">
+        <v>144</v>
+      </c>
+      <c r="D53" t="s">
+        <v>155</v>
+      </c>
+      <c r="E53" t="s">
+        <v>156</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" t="s">
+        <v>158</v>
+      </c>
+      <c r="E55" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" t="s">
+        <v>162</v>
+      </c>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" t="s">
+        <v>164</v>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" t="s">
+        <v>166</v>
+      </c>
+      <c r="F59" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60" t="s">
+        <v>146</v>
+      </c>
+      <c r="D60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" t="s">
+        <v>167</v>
+      </c>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61" t="s">
+        <v>145</v>
+      </c>
+      <c r="D61" t="s">
+        <v>108</v>
+      </c>
+      <c r="E61" t="s">
+        <v>168</v>
+      </c>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62" t="s">
+        <v>147</v>
+      </c>
+      <c r="D62" t="s">
+        <v>108</v>
+      </c>
+      <c r="E62" t="s">
+        <v>169</v>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63" t="s">
+        <v>150</v>
+      </c>
+      <c r="D63" t="s">
+        <v>170</v>
+      </c>
+      <c r="E63" t="s">
+        <v>171</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D64" t="s">
+        <v>112</v>
+      </c>
+      <c r="E64" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" t="b">
+        <v>0</v>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65" t="s">
+        <v>172</v>
+      </c>
+      <c r="D65" t="s">
+        <v>173</v>
+      </c>
+      <c r="E65" t="s">
+        <v>131</v>
+      </c>
+      <c r="F65" t="b">
+        <v>0</v>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66" t="s">
+        <v>174</v>
+      </c>
+      <c r="D66" t="s">
+        <v>138</v>
+      </c>
+      <c r="E66" t="s">
+        <v>175</v>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67" t="s">
+        <v>177</v>
+      </c>
+      <c r="D67" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" t="s">
+        <v>176</v>
+      </c>
+      <c r="F67" t="b">
+        <v>0</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="M67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68" t="s">
+        <v>178</v>
+      </c>
+      <c r="D68" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3376,5 +5947,75 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{591DDD13-37D8-4F2B-8A88-AE8A3B057132}">
+            <xm:f>Options!$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{C0BA5A44-A4FF-4230-81D5-597C1D21D3E4}">
+            <xm:f>Options!$A$3</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>F2:M68</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB124CE0-C53B-40CF-AA8F-7A5DA1081BCD}">
+          <x14:formula1>
+            <xm:f>Options!$A$2:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:M68</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2147DC-8EB6-4F95-8113-7E0BAB22461E}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>